--- a/outputs/All_States_historical_prices.xlsx
+++ b/outputs/All_States_historical_prices.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F275"/>
+  <dimension ref="A1:F276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6076,6 +6076,26 @@
       </c>
       <c r="F275" s="4" t="inlineStr"/>
     </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B276" s="3" t="n">
+        <v>82.01000000000001</v>
+      </c>
+      <c r="C276" s="3" t="n">
+        <v>87.43000000000001</v>
+      </c>
+      <c r="D276" s="3" t="n">
+        <v>82.01000000000001</v>
+      </c>
+      <c r="E276" s="3" t="n">
+        <v>87.43000000000001</v>
+      </c>
+      <c r="F276" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6087,7 +6107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F275"/>
+  <dimension ref="A1:F276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11706,6 +11726,26 @@
       </c>
       <c r="F275" s="4" t="inlineStr"/>
     </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B276" s="3" t="n">
+        <v>76.34</v>
+      </c>
+      <c r="C276" s="3" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="D276" s="3" t="n">
+        <v>76.34</v>
+      </c>
+      <c r="E276" s="3" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="F276" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11717,7 +11757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F275"/>
+  <dimension ref="A1:F276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -17336,6 +17376,26 @@
       </c>
       <c r="F275" s="4" t="inlineStr"/>
     </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B276" s="3" t="n">
+        <v>64.77</v>
+      </c>
+      <c r="C276" s="3" t="n">
+        <v>73.73999999999999</v>
+      </c>
+      <c r="D276" s="3" t="n">
+        <v>64.77</v>
+      </c>
+      <c r="E276" s="3" t="n">
+        <v>73.73999999999999</v>
+      </c>
+      <c r="F276" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17347,7 +17407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F275"/>
+  <dimension ref="A1:F276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -22966,6 +23026,26 @@
       </c>
       <c r="F275" s="4" t="inlineStr"/>
     </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B276" s="3" t="n">
+        <v>77.48999999999999</v>
+      </c>
+      <c r="C276" s="3" t="n">
+        <v>86.72</v>
+      </c>
+      <c r="D276" s="3" t="n">
+        <v>77.48999999999999</v>
+      </c>
+      <c r="E276" s="3" t="n">
+        <v>86.72</v>
+      </c>
+      <c r="F276" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22977,7 +23057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F253"/>
+  <dimension ref="A1:F254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -28156,6 +28236,26 @@
       </c>
       <c r="F253" s="4" t="inlineStr"/>
     </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="n">
+        <v>96.14</v>
+      </c>
+      <c r="C254" s="3" t="n">
+        <v>100.08</v>
+      </c>
+      <c r="D254" s="3" t="n">
+        <v>96.14</v>
+      </c>
+      <c r="E254" s="3" t="n">
+        <v>100.08</v>
+      </c>
+      <c r="F254" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/All_States_historical_prices.xlsx
+++ b/outputs/All_States_historical_prices.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F276"/>
+  <dimension ref="A1:F277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6096,6 +6096,26 @@
       </c>
       <c r="F276" s="4" t="inlineStr"/>
     </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B277" s="3" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="C277" s="3" t="n">
+        <v>86.92</v>
+      </c>
+      <c r="D277" s="3" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="E277" s="3" t="n">
+        <v>86.92</v>
+      </c>
+      <c r="F277" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6107,7 +6127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F276"/>
+  <dimension ref="A1:F277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11746,6 +11766,26 @@
       </c>
       <c r="F276" s="4" t="inlineStr"/>
     </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B277" s="3" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="C277" s="3" t="n">
+        <v>70.73</v>
+      </c>
+      <c r="D277" s="3" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="E277" s="3" t="n">
+        <v>70.73</v>
+      </c>
+      <c r="F277" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11757,7 +11797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F276"/>
+  <dimension ref="A1:F277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -17396,6 +17436,26 @@
       </c>
       <c r="F276" s="4" t="inlineStr"/>
     </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B277" s="3" t="n">
+        <v>66.81</v>
+      </c>
+      <c r="C277" s="3" t="n">
+        <v>78.04000000000001</v>
+      </c>
+      <c r="D277" s="3" t="n">
+        <v>66.81</v>
+      </c>
+      <c r="E277" s="3" t="n">
+        <v>78.04000000000001</v>
+      </c>
+      <c r="F277" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17407,7 +17467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F276"/>
+  <dimension ref="A1:F277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -23046,6 +23106,26 @@
       </c>
       <c r="F276" s="4" t="inlineStr"/>
     </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B277" s="3" t="n">
+        <v>125.73</v>
+      </c>
+      <c r="C277" s="3" t="n">
+        <v>152.96</v>
+      </c>
+      <c r="D277" s="3" t="n">
+        <v>125.73</v>
+      </c>
+      <c r="E277" s="3" t="n">
+        <v>152.96</v>
+      </c>
+      <c r="F277" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23057,7 +23137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F254"/>
+  <dimension ref="A1:F255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -28256,6 +28336,26 @@
       </c>
       <c r="F254" s="4" t="inlineStr"/>
     </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B255" s="3" t="n">
+        <v>76.83</v>
+      </c>
+      <c r="C255" s="3" t="n">
+        <v>81.73</v>
+      </c>
+      <c r="D255" s="3" t="n">
+        <v>76.83</v>
+      </c>
+      <c r="E255" s="3" t="n">
+        <v>81.73</v>
+      </c>
+      <c r="F255" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/All_States_historical_prices.xlsx
+++ b/outputs/All_States_historical_prices.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F278"/>
+  <dimension ref="A1:F279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6136,6 +6136,26 @@
       </c>
       <c r="F278" s="4" t="inlineStr"/>
     </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="B279" s="3" t="n">
+        <v>75.70999999999999</v>
+      </c>
+      <c r="C279" s="3" t="n">
+        <v>74.16</v>
+      </c>
+      <c r="D279" s="3" t="n">
+        <v>75.70999999999999</v>
+      </c>
+      <c r="E279" s="3" t="n">
+        <v>74.16</v>
+      </c>
+      <c r="F279" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6147,7 +6167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F278"/>
+  <dimension ref="A1:F279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11826,6 +11846,26 @@
       </c>
       <c r="F278" s="4" t="inlineStr"/>
     </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="B279" s="3" t="n">
+        <v>60.42</v>
+      </c>
+      <c r="C279" s="3" t="n">
+        <v>55.21</v>
+      </c>
+      <c r="D279" s="3" t="n">
+        <v>60.42</v>
+      </c>
+      <c r="E279" s="3" t="n">
+        <v>55.21</v>
+      </c>
+      <c r="F279" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11837,7 +11877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F278"/>
+  <dimension ref="A1:F279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -17516,6 +17556,26 @@
       </c>
       <c r="F278" s="4" t="inlineStr"/>
     </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="B279" s="3" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="C279" s="3" t="n">
+        <v>68.86</v>
+      </c>
+      <c r="D279" s="3" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="E279" s="3" t="n">
+        <v>68.86</v>
+      </c>
+      <c r="F279" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17527,7 +17587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F278"/>
+  <dimension ref="A1:F279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -23206,6 +23266,26 @@
       </c>
       <c r="F278" s="4" t="inlineStr"/>
     </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="B279" s="3" t="n">
+        <v>71.62</v>
+      </c>
+      <c r="C279" s="3" t="n">
+        <v>80.75</v>
+      </c>
+      <c r="D279" s="3" t="n">
+        <v>71.62</v>
+      </c>
+      <c r="E279" s="3" t="n">
+        <v>80.75</v>
+      </c>
+      <c r="F279" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23217,7 +23297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F256"/>
+  <dimension ref="A1:F257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -28456,6 +28536,26 @@
       </c>
       <c r="F256" s="4" t="inlineStr"/>
     </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="B257" s="3" t="n">
+        <v>57.95</v>
+      </c>
+      <c r="C257" s="3" t="n">
+        <v>65.81</v>
+      </c>
+      <c r="D257" s="3" t="n">
+        <v>57.95</v>
+      </c>
+      <c r="E257" s="3" t="n">
+        <v>65.81</v>
+      </c>
+      <c r="F257" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/All_States_historical_prices.xlsx
+++ b/outputs/All_States_historical_prices.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F279"/>
+  <dimension ref="A1:F280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6156,6 +6156,26 @@
       </c>
       <c r="F279" s="4" t="inlineStr"/>
     </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="B280" s="3" t="n">
+        <v>65.31999999999999</v>
+      </c>
+      <c r="C280" s="3" t="n">
+        <v>59.01</v>
+      </c>
+      <c r="D280" s="3" t="n">
+        <v>65.31999999999999</v>
+      </c>
+      <c r="E280" s="3" t="n">
+        <v>59.01</v>
+      </c>
+      <c r="F280" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6167,7 +6187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F279"/>
+  <dimension ref="A1:F280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11866,6 +11886,26 @@
       </c>
       <c r="F279" s="4" t="inlineStr"/>
     </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="B280" s="3" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="C280" s="3" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="D280" s="3" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="E280" s="3" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="F280" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11877,7 +11917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F279"/>
+  <dimension ref="A1:F280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -17576,6 +17616,26 @@
       </c>
       <c r="F279" s="4" t="inlineStr"/>
     </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="B280" s="3" t="n">
+        <v>36.83</v>
+      </c>
+      <c r="C280" s="3" t="n">
+        <v>36.93</v>
+      </c>
+      <c r="D280" s="3" t="n">
+        <v>36.83</v>
+      </c>
+      <c r="E280" s="3" t="n">
+        <v>36.93</v>
+      </c>
+      <c r="F280" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17587,7 +17647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F279"/>
+  <dimension ref="A1:F280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -23286,6 +23346,26 @@
       </c>
       <c r="F279" s="4" t="inlineStr"/>
     </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="B280" s="3" t="n">
+        <v>37.71</v>
+      </c>
+      <c r="C280" s="3" t="n">
+        <v>34.31</v>
+      </c>
+      <c r="D280" s="3" t="n">
+        <v>37.71</v>
+      </c>
+      <c r="E280" s="3" t="n">
+        <v>34.31</v>
+      </c>
+      <c r="F280" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23297,7 +23377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F257"/>
+  <dimension ref="A1:F258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -28556,6 +28636,26 @@
       </c>
       <c r="F257" s="4" t="inlineStr"/>
     </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="n">
+        <v>38.86</v>
+      </c>
+      <c r="C258" s="3" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="D258" s="3" t="n">
+        <v>38.86</v>
+      </c>
+      <c r="E258" s="3" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="F258" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
